--- a/MU/Test upload format/CG fee reduction/2026 - 2027 - SHG/Q2 26-27 SHG.xlsx
+++ b/MU/Test upload format/CG fee reduction/2026 - 2027 - SHG/Q2 26-27 SHG.xlsx
@@ -89,7 +89,7 @@
     <t>sancdt</t>
   </si>
   <si>
-    <t>frstdisamt</t>
+    <t>totalfrstdisamt</t>
   </si>
   <si>
     <t>frstdisdt</t>
